--- a/diseases/d120/1995-1999.xlsx
+++ b/diseases/d120/1995-1999.xlsx
@@ -6743,6 +6743,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7763,6 +7768,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8544,6 +8554,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9325,6 +9340,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10106,6 +10126,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10887,6 +10912,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11668,6 +11698,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12449,6 +12484,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13230,6 +13270,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14011,6 +14056,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14792,6 +14842,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15573,6 +15628,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16744,6 +16804,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17764,6 +17829,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18545,6 +18615,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19326,6 +19401,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20107,6 +20187,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20888,6 +20973,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21669,6 +21759,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22450,6 +22545,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23231,6 +23331,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24012,6 +24117,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24793,6 +24903,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25574,6 +25689,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26745,6 +26865,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27765,6 +27890,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28546,6 +28676,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29327,6 +29462,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30108,6 +30248,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30889,6 +31034,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31670,6 +31820,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32451,6 +32606,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33232,6 +33392,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34013,6 +34178,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34794,6 +34964,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35573,6 +35748,11 @@
       <c r="S179" t="inlineStr">
         <is>
           <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">

--- a/diseases/d120/1995-1999.xlsx
+++ b/diseases/d120/1995-1999.xlsx
@@ -6738,6 +6738,11 @@
       <c r="Q32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6750,12 +6755,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -7748,6 +7763,11 @@
       <c r="Q37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7760,12 +7780,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -8519,6 +8549,11 @@
       <c r="Q41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8531,12 +8566,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -9290,6 +9335,11 @@
       <c r="Q45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9302,12 +9352,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -10061,6 +10121,11 @@
       <c r="Q49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10073,12 +10138,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -10832,6 +10907,11 @@
       <c r="Q53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10844,12 +10924,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -11603,6 +11693,11 @@
       <c r="Q57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11615,12 +11710,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -12374,6 +12479,11 @@
       <c r="Q61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12386,12 +12496,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -13145,6 +13265,11 @@
       <c r="Q65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13157,12 +13282,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -13916,6 +14051,11 @@
       <c r="Q69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13928,12 +14068,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -14687,6 +14837,11 @@
       <c r="Q73" t="n">
         <v>0</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14699,12 +14854,22 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -15458,6 +15623,11 @@
       <c r="Q77" t="n">
         <v>0</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15470,12 +15640,22 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -16619,6 +16799,11 @@
       <c r="Q83" t="n">
         <v>0</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16631,12 +16816,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -17629,6 +17824,11 @@
       <c r="Q88" t="n">
         <v>0</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17641,12 +17841,22 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -18400,6 +18610,11 @@
       <c r="Q92" t="n">
         <v>0</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18412,12 +18627,22 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -19171,6 +19396,11 @@
       <c r="Q96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19183,12 +19413,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -19942,6 +20182,11 @@
       <c r="Q100" t="n">
         <v>0</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19954,12 +20199,22 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -20713,6 +20968,11 @@
       <c r="Q104" t="n">
         <v>0</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20725,12 +20985,22 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -21484,6 +21754,11 @@
       <c r="Q108" t="n">
         <v>0</v>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21496,12 +21771,22 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -22255,6 +22540,11 @@
       <c r="Q112" t="n">
         <v>0</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22267,12 +22557,22 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -23026,6 +23326,11 @@
       <c r="Q116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23038,12 +23343,22 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -23797,6 +24112,11 @@
       <c r="Q120" t="n">
         <v>0</v>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23809,12 +24129,22 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -24568,6 +24898,11 @@
       <c r="Q124" t="n">
         <v>0</v>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24580,12 +24915,22 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -25339,6 +25684,11 @@
       <c r="Q128" t="n">
         <v>0</v>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25351,12 +25701,22 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -26500,6 +26860,11 @@
       <c r="Q134" t="n">
         <v>0</v>
       </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26512,12 +26877,22 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -27510,6 +27885,11 @@
       <c r="Q139" t="n">
         <v>0</v>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27522,12 +27902,22 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -28281,6 +28671,11 @@
       <c r="Q143" t="n">
         <v>0</v>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28293,12 +28688,22 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -29052,6 +29457,11 @@
       <c r="Q147" t="n">
         <v>0</v>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29064,12 +29474,22 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -29823,6 +30243,11 @@
       <c r="Q151" t="n">
         <v>0</v>
       </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29835,12 +30260,22 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -30594,6 +31029,11 @@
       <c r="Q155" t="n">
         <v>0</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30606,12 +31046,22 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -31365,6 +31815,11 @@
       <c r="Q159" t="n">
         <v>0</v>
       </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31377,12 +31832,22 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -32136,6 +32601,11 @@
       <c r="Q163" t="n">
         <v>0</v>
       </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32148,12 +32618,22 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -32907,6 +33387,11 @@
       <c r="Q167" t="n">
         <v>0</v>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32919,12 +33404,22 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -33678,6 +34173,11 @@
       <c r="Q171" t="n">
         <v>0</v>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33690,12 +34190,22 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -34449,6 +34959,11 @@
       <c r="Q175" t="n">
         <v>0</v>
       </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34461,12 +34976,22 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
         <v>0</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -35220,6 +35745,11 @@
       <c r="Q179" t="n">
         <v>0</v>
       </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35232,12 +35762,22 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
         <v>0</v>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
